--- a/reports/telegram/aegis_daily_2026-08-25.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-25.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV27"/>
+  <dimension ref="A1:AV28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>79.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       </c>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD · 17d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 34% · band HOLD→STRONG · 17d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr"/>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>31.9</v>
+        <v>34.3</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
@@ -828,53 +828,53 @@
         </is>
       </c>
       <c r="AC2" s="3" t="n">
-        <v>582</v>
+        <v>594.5</v>
       </c>
       <c r="AD2" s="3" t="n">
         <v>553.3</v>
       </c>
       <c r="AE2" s="3" t="n">
-        <v>576.1799999999999</v>
+        <v>588.55</v>
       </c>
       <c r="AF2" s="3" t="n">
-        <v>587.8200000000001</v>
+        <v>600.45</v>
       </c>
       <c r="AG2" s="3" t="n">
-        <v>547.08</v>
+        <v>558.83</v>
       </c>
       <c r="AH2" s="3" t="n">
-        <v>-1.12</v>
+        <v>1</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>651.84</v>
+        <v>665.84</v>
       </c>
       <c r="AJ2" s="3" t="n">
-        <v>17.81</v>
+        <v>20.34</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>721.6799999999999</v>
+        <v>737.1799999999999</v>
       </c>
       <c r="AL2" s="3" t="n">
-        <v>30.43</v>
+        <v>33.23</v>
       </c>
       <c r="AM2" s="3" t="n">
-        <v>582.8</v>
+        <v>582</v>
       </c>
       <c r="AN2" s="3" t="n">
-        <v>-0.14</v>
+        <v>2.15</v>
       </c>
       <c r="AO2" s="3" t="n">
-        <v>5.19</v>
+        <v>7.45</v>
       </c>
       <c r="AP2" s="3" t="n">
-        <v>5.19</v>
+        <v>7.45</v>
       </c>
       <c r="AQ2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Value · Growth · Trend</t>
+          <t>Value · Trend · Ai Hybrid</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr"/>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260804-bfcaee</t>
+          <t>R2-TATACOMM-IND-20260825-759557</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260804</t>
+          <t>TATACOMM_IND_20260825</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -913,48 +913,60 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ICICI Bank</t>
-        </is>
-      </c>
+          <t>TATACOMM</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>→ GNFC.NS · +57.6pp alpha</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr"/>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.6%) · Rank ↑ 2→1 · Conf 82% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🔴 AVOID · Rank #11 · Conf 22% · band EXIT · 60d left · → EXIT (rotate to GNFC.NS)</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>82</v>
+        <v>21.5</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -962,61 +974,63 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="X3" s="3" t="inlineStr"/>
+        <v>-23.2</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="AD3" s="3" t="n">
+        <v>1702.7</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>1685.67</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>1719.73</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>1617.57</v>
+      </c>
+      <c r="AH3" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>1838.92</v>
+      </c>
+      <c r="AJ3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK3" s="3" t="n">
+        <v>1958.1</v>
+      </c>
+      <c r="AL3" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>91</v>
-      </c>
-      <c r="AB3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="n">
-        <v>1420.5</v>
-      </c>
-      <c r="AD3" s="3" t="n">
-        <v>1438.5</v>
-      </c>
-      <c r="AE3" s="3" t="n">
-        <v>1382</v>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>1459</v>
-      </c>
-      <c r="AG3" s="3" t="n">
-        <v>1349.475</v>
-      </c>
-      <c r="AH3" s="3" t="n">
-        <v>-6.19</v>
-      </c>
-      <c r="AI3" s="3" t="n">
-        <v>1496</v>
-      </c>
-      <c r="AJ3" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK3" s="3" t="n">
-        <v>1600.72</v>
-      </c>
-      <c r="AL3" s="3" t="n">
-        <v>11.28</v>
-      </c>
       <c r="AM3" s="3" t="n">
-        <v>1420</v>
+        <v>1660</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>0.04</v>
+        <v>2.57</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="AP3" s="3" t="n">
         <v>0</v>
@@ -1024,33 +1038,31 @@
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr"/>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
       <c r="AU3" s="3" t="n">
-        <v>4</v>
+        <v>57.58</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-SUNPHARMA-IND-20260804-22e939</t>
+          <t>R1-ICICIBANK-IND-20260804-bfcaee</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA_IND_20260804</t>
+          <t>ICICIBANK_IND_20260804</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1070,12 +1082,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Sun Pharma</t>
+          <t>ICICI Bank</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1086,13 +1098,13 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="M4" s="3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
@@ -1101,16 +1113,12 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 87% · momentum → · 91d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.6% ≤ -5.0% · exit</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 82% · momentum → · 91d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr"/>
       <c r="U4" s="3" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1118,7 +1126,7 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
@@ -1136,43 +1144,43 @@
         </is>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>1902.4</v>
+        <v>1417.9</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>2014.8</v>
+        <v>1438.5</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1851</v>
+        <v>1379</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1954</v>
+        <v>1457</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>1807.28</v>
+        <v>1347.005</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-10.3</v>
+        <v>-6.36</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1990</v>
+        <v>1493</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>-1.23</v>
+        <v>3.79</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>2129.3</v>
+        <v>1597.51</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>5.68</v>
+        <v>11.05</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1902.4</v>
+        <v>1420.5</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-5.58</v>
+        <v>-1.43</v>
       </c>
       <c r="AP4" s="3" t="n">
         <v>0</v>
@@ -1183,30 +1191,30 @@
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="AT4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>-1.23</v>
+        <v>3.79</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-PIDILITIND-IND-20260804-c2e1ef</t>
+          <t>R1-SUNPHARMA-IND-20260804-22e939</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND_IND_20260804</t>
+          <t>SUNPHARMA_IND_20260804</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1226,12 +1234,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Pidilite</t>
+          <t>Sun Pharma</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1242,13 +1250,13 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
@@ -1257,12 +1265,16 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank → 3→3 · Conf 86% · momentum → · 91d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 87% · momentum → · 91d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
       <c r="U5" s="3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1270,7 +1282,7 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
@@ -1288,43 +1300,43 @@
         </is>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>1646</v>
+        <v>1912.7</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>1625.5</v>
+        <v>2014.8</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>1593</v>
+        <v>1861</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1699</v>
+        <v>1964</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1563.7</v>
+        <v>1817.065</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-3.8</v>
+        <v>-9.81</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>1668</v>
+        <v>2000</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>2.61</v>
+        <v>-0.73</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>1784.76</v>
+        <v>2140</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>6.21</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1649</v>
+        <v>1902.4</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>-0.18</v>
+        <v>0.54</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>1.26</v>
+        <v>-5.07</v>
       </c>
       <c r="AP5" s="3" t="n">
         <v>0</v>
@@ -1335,30 +1347,30 @@
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="AT5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>2.61</v>
+        <v>-0.73</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-NTPC-IND-20260804-11a3e5</t>
+          <t>R1-PIDILITIND-IND-20260804-c2e1ef</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>NTPC_IND_20260804</t>
+          <t>PIDILITIND_IND_20260804</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1378,26 +1390,26 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>Pidilite</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>STRONG BUY</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -1409,12 +1421,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.4%) · Rank → 4→4 · Conf 72% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-3.1%) · Rank → 3→3 · Conf 86% · momentum → · 91d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1422,7 +1434,7 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
@@ -1440,43 +1452,43 @@
         </is>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>340.7</v>
+        <v>1654.9</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>345.75</v>
+        <v>1625.5</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>332</v>
+        <v>1602</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>349</v>
+        <v>1708</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>323.665</v>
+        <v>1572.155</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-6.39</v>
+        <v>-3.28</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>367.956</v>
+        <v>1677</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>6.42</v>
+        <v>3.17</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>393.7129200000001</v>
+        <v>1794.39</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>13.87</v>
+        <v>10.39</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>340</v>
+        <v>1646</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.21</v>
+        <v>0.54</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>-1.46</v>
+        <v>1.81</v>
       </c>
       <c r="AP6" s="3" t="n">
         <v>0</v>
@@ -1487,30 +1499,30 @@
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>6.42</v>
+        <v>3.17</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260805-6a4927</t>
+          <t>R1-NTPC-IND-20260804-11a3e5</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260805</t>
+          <t>NTPC_IND_20260804</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1530,12 +1542,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Lupin</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1546,13 +1558,13 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
@@ -1561,16 +1573,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→5 · Conf 67% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-9.0% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-2.3%) · Rank → 4→4 · Conf 71% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr"/>
       <c r="U7" s="3" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1578,11 +1586,11 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>90</v>
@@ -1592,50 +1600,50 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>2199.8</v>
+        <v>338</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>2417</v>
+        <v>345.75</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>2142</v>
+        <v>330</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>2257</v>
+        <v>346</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>2089.81</v>
+        <v>321.1</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-13.54</v>
+        <v>-7.13</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>2375.784000000001</v>
+        <v>365.04</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>-1.71</v>
+        <v>5.58</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>2542.088880000001</v>
+        <v>390.5928000000001</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>5.18</v>
+        <v>12.97</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>2201.8</v>
+        <v>340.7</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.79</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-8.99</v>
+        <v>-2.24</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0</v>
@@ -1643,30 +1651,30 @@
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="AT7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>-1.71</v>
+        <v>5.58</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-POWERGRID-IND-20260805-486b96</t>
+          <t>R1-LUPIN-IND-20260805-6a4927</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID_IND_20260805</t>
+          <t>LUPIN_IND_20260805</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1686,12 +1694,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Power Grid</t>
+          <t>Lupin</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1702,13 +1710,13 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
@@ -1717,12 +1725,16 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.1%) · Rank ↑ 7→6 · Conf 69% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→5 · Conf 67% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-10.0% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="U8" s="3" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1730,7 +1742,7 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
@@ -1748,46 +1760,46 @@
         </is>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>274</v>
+        <v>2175.4</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>285.9</v>
+        <v>2417</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>268</v>
+        <v>2119</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>280</v>
+        <v>2232</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>260.3</v>
+        <v>2066.63</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>-8.949999999999999</v>
+        <v>-14.5</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>295.92</v>
+        <v>2349.432</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>3.5</v>
+        <v>-2.8</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>316.6344</v>
+        <v>2513.892240000001</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>10.75</v>
+        <v>4.01</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>272.4</v>
+        <v>2199.8</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>0.59</v>
+        <v>-1.11</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-4.16</v>
+        <v>-10</v>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ8" s="3" t="n">
         <v>0</v>
@@ -1795,18 +1807,18 @@
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>3.5</v>
+        <v>-2.8</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
@@ -1854,13 +1866,13 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
@@ -1869,7 +1881,7 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↑ 8→7 · Conf 66% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↑ 8→6 · Conf 66% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr"/>
@@ -1900,43 +1912,43 @@
         </is>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>414.3</v>
+        <v>408.3</v>
       </c>
       <c r="AD9" s="3" t="n">
         <v>388.7</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>393.585</v>
+        <v>387.885</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>1.26</v>
+        <v>-0.21</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>447.444</v>
+        <v>440.9640000000001</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>15.11</v>
+        <v>13.45</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>478.7650800000001</v>
+        <v>471.8314800000001</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>23.17</v>
+        <v>21.39</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>414</v>
+        <v>414.3</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>6.59</v>
+        <v>5.04</v>
       </c>
       <c r="AP9" s="3" t="n">
         <v>0</v>
@@ -1954,23 +1966,23 @@
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>15.11</v>
+        <v>13.45</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260805-292818</t>
+          <t>R1-POWERGRID-IND-20260805-486b96</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260805</t>
+          <t>POWERGRID_IND_20260805</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1990,12 +2002,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Coal India</t>
+          <t>Power Grid</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -2006,13 +2018,13 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr"/>
@@ -2021,12 +2033,16 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↑ 10→8 · Conf 66% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 7→7 · Conf 69% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
       <c r="U10" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2034,7 +2050,7 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
@@ -2052,77 +2068,77 @@
         </is>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>406</v>
+        <v>270.2</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>411.3</v>
+        <v>285.9</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>394</v>
+        <v>264</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>418</v>
+        <v>277</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>385.7</v>
+        <v>256.69</v>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>-6.22</v>
+        <v>-10.22</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>438.48</v>
+        <v>291.816</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>6.61</v>
+        <v>2.07</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>469.1736</v>
+        <v>312.24312</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>14.07</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>405.2</v>
+        <v>274</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>0.2</v>
+        <v>-1.39</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-1.29</v>
+        <v>-5.49</v>
       </c>
       <c r="AP10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>6.61</v>
+        <v>2.07</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260804-9c1ab0</t>
+          <t>R1-ONGC-IND-20260811-f86a0f</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260804</t>
+          <t>ONGC_IND_20260811</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2142,30 +2158,22 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>IRCTC</t>
-        </is>
-      </c>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>2</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
@@ -2173,12 +2181,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↓ 7→9 · Conf 66% · momentum → · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank #8 · Conf 67% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2186,11 +2194,11 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>90</v>
@@ -2200,81 +2208,77 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>484.2</v>
+        <v>235.9</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>494.35</v>
+        <v>239.4499969482422</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>470</v>
+        <v>229</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>499</v>
+        <v>243</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>459.99</v>
+        <v>224.105</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>-6.95</v>
+        <v>-6.41</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>522.936</v>
+        <v>254.772</v>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>5.78</v>
+        <v>6.4</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>559.5415200000001</v>
+        <v>272.6060400000001</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>13.19</v>
+        <v>13.85</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>484.2</v>
+        <v>237</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AP11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.48</v>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr"/>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="AT11" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>5.78</v>
+        <v>6.4</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-IRCTC-IND-20260804-9c1ab0</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>IRCTC_IND_20260804</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2294,22 +2298,30 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
@@ -2317,7 +2329,7 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank #10 · Conf 66% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 7→9 · Conf 66% · momentum → · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
@@ -2330,11 +2342,11 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>90</v>
@@ -2344,77 +2356,81 @@
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>237</v>
+        <v>483.5</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>239.4499969482422</v>
+        <v>494.35</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>230</v>
+        <v>469</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>244</v>
+        <v>498</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>225.15</v>
+        <v>459.325</v>
       </c>
       <c r="AH12" s="3" t="n">
-        <v>-5.97</v>
+        <v>-7.09</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>255.96</v>
+        <v>522.1800000000001</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>6.89</v>
+        <v>5.63</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>273.8772</v>
+        <v>558.7326</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>14.38</v>
+        <v>13.02</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>236.4</v>
+        <v>484.2</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>0.25</v>
+        <v>-0.14</v>
       </c>
       <c r="AO12" s="3" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="AP12" s="3" t="inlineStr"/>
-      <c r="AQ12" s="3" t="inlineStr"/>
+        <v>-2.19</v>
+      </c>
+      <c r="AP12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR12" s="3" t="inlineStr"/>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="AT12" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>6.89</v>
+        <v>5.63</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R1-ITC-IND-20260805-bb820d</t>
+          <t>R1-COALINDIA-IND-20260805-292818</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260805</t>
+          <t>COALINDIA_IND_20260805</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2434,12 +2450,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Coal India</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2450,10 +2466,14 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
@@ -2461,12 +2481,12 @@
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.3%) · Rank #11 · Conf 70% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank → 10→10 · Conf 66% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2492,77 +2512,77 @@
         </is>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>270.6</v>
+        <v>405.8</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>282.9</v>
+        <v>411.3</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>264</v>
+        <v>394</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>277</v>
+        <v>418</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>257.07</v>
+        <v>385.51</v>
       </c>
       <c r="AH13" s="3" t="n">
-        <v>-9.130000000000001</v>
+        <v>-6.27</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>271</v>
+        <v>438.2640000000001</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>-4.21</v>
+        <v>6.56</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>289.97</v>
+        <v>468.9424800000001</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>2.5</v>
+        <v>14.01</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>269.4</v>
+        <v>406</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>0.45</v>
+        <v>-0.05</v>
       </c>
       <c r="AO13" s="3" t="n">
-        <v>-4.35</v>
+        <v>-1.34</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="AT13" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>-4.21</v>
+        <v>6.56</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R1-HINDUNILVR-IND-20260812-d25c10</t>
+          <t>R1-ITC-IND-20260805-bb820d</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR_IND_20260812</t>
+          <t>ITC_IND_20260805</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2582,19 +2602,23 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
@@ -2605,12 +2629,16 @@
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank #12 · Conf 65% · momentum → · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.2%) · Rank #11 · Conf 70% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.3% ≤ -5.0% · exit</t>
+        </is>
+      </c>
       <c r="U14" s="3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2618,11 +2646,11 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>90</v>
@@ -2632,50 +2660,54 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>2019.9</v>
+        <v>268</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>2064.89990234375</v>
+        <v>282.9</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>1959</v>
+        <v>262</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>2081</v>
+        <v>274</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>1918.905</v>
+        <v>254.6</v>
       </c>
       <c r="AH14" s="3" t="n">
-        <v>-7.07</v>
+        <v>-10</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>2181.492</v>
+        <v>269</v>
       </c>
       <c r="AJ14" s="3" t="n">
-        <v>5.65</v>
+        <v>-4.91</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>2334.19644</v>
+        <v>287.83</v>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>13.04</v>
+        <v>1.74</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>2015</v>
+        <v>270.6</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>0.24</v>
+        <v>-0.96</v>
       </c>
       <c r="AO14" s="3" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="AP14" s="3" t="inlineStr"/>
-      <c r="AQ14" s="3" t="inlineStr"/>
+        <v>-5.27</v>
+      </c>
+      <c r="AP14" s="3" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AQ14" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr">
         <is>
@@ -2686,23 +2718,23 @@
         <v>5</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>5.65</v>
+        <v>-4.91</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R2-LUPIN-IND-20260804-80ded8</t>
+          <t>R1-HINDUNILVR-IND-20260812-d25c10</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260804</t>
+          <t>HINDUNILVR_IND_20260812</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2717,19 +2749,15 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Lupin</t>
-        </is>
-      </c>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2738,14 +2766,10 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr"/>
@@ -2753,12 +2777,12 @@
       <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.0%) · Rank #12 · Conf 65% · momentum → · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>51.8</v>
+        <v>65</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2766,89 +2790,91 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>61</v>
+        <v>91</v>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>2417</v>
+        <v>2019.3</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>2417</v>
+        <v>2064.89990234375</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>2392.83</v>
+        <v>1958</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>2441.17</v>
+        <v>2081</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>2296.15</v>
+        <v>1918.335</v>
       </c>
       <c r="AH15" s="3" t="n">
-        <v>-5</v>
+        <v>-7.1</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>2610.36</v>
+        <v>2180.844</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>8</v>
+        <v>5.61</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>2779.55</v>
+        <v>2333.50308</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>15</v>
+        <v>13.01</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>2201.8</v>
+        <v>2019.9</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AQ15" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-2.21</v>
+      </c>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr"/>
-      <c r="AT15" s="3" t="inlineStr"/>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU15" s="3" t="n">
-        <v>8</v>
+        <v>5.61</v>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R2-LUPIN-IND-20260804-80ded8</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>LUPIN_IND_20260804</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2868,12 +2894,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Chambal Fert.</t>
+          <t>Lupin</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2884,13 +2910,13 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr"/>
@@ -2899,12 +2925,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>38.3</v>
+        <v>51.8</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2912,7 +2938,7 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>22.4</v>
+        <v>26</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
@@ -2930,46 +2956,46 @@
         </is>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>443.35</v>
+        <v>2417</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>443.35</v>
+        <v>2417</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>438.92</v>
+        <v>2392.83</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>447.78</v>
+        <v>2441.17</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>421.1825</v>
+        <v>2296.15</v>
       </c>
       <c r="AH16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>478.818</v>
+        <v>2610.36</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>509.8525</v>
+        <v>2779.55</v>
       </c>
       <c r="AL16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>431.15</v>
+        <v>2199.8</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>0.1</v>
+        <v>-1.11</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>2.54</v>
+        <v>1.24</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>0</v>
@@ -2982,19 +3008,19 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>CHAMBLFERT_IND_20260804</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3014,12 +3040,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Punjab Natl. Bank</t>
+          <t>Chambal Fert.</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -3030,13 +3056,13 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr"/>
@@ -3045,12 +3071,12 @@
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>32.1</v>
+        <v>38.3</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3058,7 +3084,7 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>22.2</v>
+        <v>22.4</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
@@ -3076,49 +3102,49 @@
         </is>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>113.36</v>
+        <v>443.35</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>113.36</v>
+        <v>443.35</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>112.23</v>
+        <v>438.92</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>114.49</v>
+        <v>447.78</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>107.692</v>
+        <v>421.1825</v>
       </c>
       <c r="AH17" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>122.4288</v>
+        <v>478.818</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>130.364</v>
+        <v>509.8525</v>
       </c>
       <c r="AL17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>116.55</v>
+        <v>431.6</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>-0.04</v>
+        <v>1.4</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP17" s="3" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>-2.01</v>
+        <v>0</v>
       </c>
       <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="3" t="inlineStr"/>
@@ -3128,19 +3154,19 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R2-COALINDIA-IND-20260804-12bb5e</t>
+          <t>R2-PNB-IND-20260804-c7957c</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260804</t>
+          <t>PNB_IND_20260804</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3160,12 +3186,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Coal India</t>
+          <t>Punjab Natl. Bank</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -3176,10 +3202,10 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
@@ -3191,12 +3217,12 @@
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>36.1</v>
+        <v>32.1</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3222,40 +3248,40 @@
         </is>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>411.3</v>
+        <v>113.36</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>411.3</v>
+        <v>113.36</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>407.19</v>
+        <v>112.23</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>415.41</v>
+        <v>114.49</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>390.735</v>
+        <v>107.692</v>
       </c>
       <c r="AH18" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>444.2040000000001</v>
+        <v>122.4288</v>
       </c>
       <c r="AJ18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>472.995</v>
+        <v>130.364</v>
       </c>
       <c r="AL18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>405.2</v>
+        <v>116.5</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>0.2</v>
+        <v>-0.61</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>0</v>
@@ -3264,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>-0.3</v>
+        <v>-2.01</v>
       </c>
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr"/>
@@ -3274,19 +3300,19 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R2-COALINDIA-IND-20260804-12bb5e</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>COALINDIA_IND_20260804</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3306,12 +3332,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Coal India</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3322,13 +3348,13 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr"/>
@@ -3337,12 +3363,12 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>38.3</v>
+        <v>36.1</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3350,7 +3376,7 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
@@ -3368,49 +3394,49 @@
         </is>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>282.9</v>
+        <v>411.3</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>282.9</v>
+        <v>411.3</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>280.07</v>
+        <v>407.19</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>285.73</v>
+        <v>415.41</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>390.735</v>
       </c>
       <c r="AH19" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>305.532</v>
+        <v>444.2040000000001</v>
       </c>
       <c r="AJ19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>472.995</v>
       </c>
       <c r="AL19" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>269.4</v>
+        <v>406</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>0.45</v>
+        <v>-0.05</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP19" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ19" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AR19" s="3" t="inlineStr"/>
       <c r="AS19" s="3" t="inlineStr"/>
@@ -3420,19 +3446,19 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R2-ITC-IND-20260804-a049df</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>ITC_IND_20260804</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3452,12 +3478,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Bata India</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3468,13 +3494,13 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr"/>
@@ -3483,12 +3509,12 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>24</v>
+        <v>38.3</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3496,7 +3522,7 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>-30.3</v>
+        <v>21.6</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
@@ -3514,49 +3540,49 @@
         </is>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>709</v>
+        <v>282.9</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>709</v>
+        <v>282.9</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>701.91</v>
+        <v>280.07</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>716.09</v>
+        <v>285.73</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>673.55</v>
+        <v>268.7549999999999</v>
       </c>
       <c r="AH20" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>765.72</v>
+        <v>305.532</v>
       </c>
       <c r="AJ20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>325.3349999999999</v>
       </c>
       <c r="AL20" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM20" s="3" t="n">
-        <v>701.05</v>
+        <v>270.6</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>0.19</v>
+        <v>-0.96</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP20" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AQ20" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR20" s="3" t="inlineStr"/>
       <c r="AS20" s="3" t="inlineStr"/>
@@ -3566,19 +3592,19 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R2-BATAINDIA-IND-20260804-21b729</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>BATAINDIA_IND_20260804</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3598,10 +3624,14 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr"/>
+          <t>BATAINDIA</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Bata India</t>
+        </is>
+      </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3610,10 +3640,10 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -3625,12 +3655,12 @@
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>40.7</v>
+        <v>24</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -3638,11 +3668,11 @@
         </is>
       </c>
       <c r="W21" s="3" t="n">
-        <v>23.8</v>
+        <v>-30.3</v>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>60</v>
@@ -3652,53 +3682,53 @@
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>5322.4</v>
+        <v>709</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>5322.4</v>
+        <v>709</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>5269.18</v>
+        <v>701.91</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>5375.62</v>
+        <v>716.09</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>5056.28</v>
+        <v>673.55</v>
       </c>
       <c r="AH21" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>5748.192</v>
+        <v>765.72</v>
       </c>
       <c r="AJ21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>815.3499999999999</v>
       </c>
       <c r="AL21" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM21" s="3" t="n">
-        <v>5667.5</v>
+        <v>702.35</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>0.46</v>
+        <v>-2.5</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP21" s="3" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AR21" s="3" t="inlineStr"/>
       <c r="AS21" s="3" t="inlineStr"/>
@@ -3708,19 +3738,19 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>PERSISTENT_IND_20260805</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3740,7 +3770,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
@@ -3752,10 +3782,10 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -3767,12 +3797,12 @@
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="n">
-        <v>38.3</v>
+        <v>40.7</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
@@ -3780,7 +3810,7 @@
         </is>
       </c>
       <c r="W22" s="3" t="n">
-        <v>20.7</v>
+        <v>23.8</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
@@ -3798,46 +3828,46 @@
         </is>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>11127</v>
+        <v>5322.4</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>11127</v>
+        <v>5322.4</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>11015.73</v>
+        <v>5269.18</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>11238.27</v>
+        <v>5375.62</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>10570.65</v>
+        <v>5056.28</v>
       </c>
       <c r="AH22" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>12017.16</v>
+        <v>5748.192</v>
       </c>
       <c r="AJ22" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>12796.05</v>
+        <v>6120.759999999999</v>
       </c>
       <c r="AL22" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM22" s="3" t="n">
-        <v>11320</v>
+        <v>5693.5</v>
       </c>
       <c r="AN22" s="3" t="n">
-        <v>-0.62</v>
+        <v>-1.36</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP22" s="3" t="n">
-        <v>3.69</v>
+        <v>3.32</v>
       </c>
       <c r="AQ22" s="3" t="n">
         <v>0</v>
@@ -3850,19 +3880,19 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>R2-LICI-IND-20260805-a4f409</t>
+          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LICI_IND_20260805</t>
+          <t>BAJAJHLDNG_IND_20260805</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3882,7 +3912,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -3894,10 +3924,14 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr"/>
@@ -3905,12 +3939,12 @@
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="n">
-        <v>37.2</v>
+        <v>38.3</v>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
@@ -3918,7 +3952,7 @@
         </is>
       </c>
       <c r="W23" s="3" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
@@ -3936,46 +3970,46 @@
         </is>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>391.3</v>
+        <v>11127</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>391.3</v>
+        <v>11127</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>387.39</v>
+        <v>11015.73</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>395.21</v>
+        <v>11238.27</v>
       </c>
       <c r="AG23" s="3" t="n">
-        <v>371.735</v>
+        <v>10570.65</v>
       </c>
       <c r="AH23" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>422.604</v>
+        <v>12017.16</v>
       </c>
       <c r="AJ23" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>449.995</v>
+        <v>12796.05</v>
       </c>
       <c r="AL23" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM23" s="3" t="n">
-        <v>422.25</v>
+        <v>11250</v>
       </c>
       <c r="AN23" s="3" t="n">
-        <v>0.89</v>
+        <v>-0.97</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP23" s="3" t="n">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="AQ23" s="3" t="n">
         <v>0</v>
@@ -3988,19 +4022,19 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R2-LICI-IND-20260805-a4f409</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>LICI_IND_20260805</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4020,7 +4054,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -4032,7 +4066,7 @@
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
@@ -4043,12 +4077,12 @@
       <c r="R24" s="3" t="inlineStr"/>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="3" t="n">
-        <v>21.5</v>
+        <v>37.2</v>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
@@ -4056,7 +4090,7 @@
         </is>
       </c>
       <c r="W24" s="3" t="n">
-        <v>-25.9</v>
+        <v>20.6</v>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="n">
@@ -4074,40 +4108,40 @@
         </is>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>2744.3</v>
+        <v>391.3</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>2744.3</v>
+        <v>391.3</v>
       </c>
       <c r="AE24" s="3" t="n">
-        <v>2716.86</v>
+        <v>387.39</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>2771.74</v>
+        <v>395.21</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>2607.085</v>
+        <v>371.735</v>
       </c>
       <c r="AH24" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>2963.844000000001</v>
+        <v>422.604</v>
       </c>
       <c r="AJ24" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>3155.945</v>
+        <v>449.995</v>
       </c>
       <c r="AL24" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM24" s="3" t="n">
-        <v>2885.8</v>
+        <v>426</v>
       </c>
       <c r="AN24" s="3" t="n">
-        <v>-0.35</v>
+        <v>-0.08</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>0</v>
@@ -4126,19 +4160,19 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>R1-KOTAKBANK-IND-20260804-5087ff</t>
+          <t>R2-TIINDIA-IND-20260805-44fbae</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK_IND_20260804</t>
+          <t>TIINDIA_IND_20260805</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4153,19 +4187,15 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Kotak Bank</t>
-        </is>
-      </c>
+          <t>TIINDIA</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4174,41 +4204,23 @@
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n">
-        <v>83.8</v>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="Q25" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
+      <c r="N25" s="3" t="inlineStr"/>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr"/>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>🟡 WAIT (Δ+2.6%) · Rank → 5→5 · Conf 71% · momentum → · band STRONG · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr"/>
       <c r="U25" s="3" t="n">
-        <v>71</v>
+        <v>21.5</v>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
@@ -4216,11 +4228,11 @@
         </is>
       </c>
       <c r="W25" s="3" t="n">
-        <v>63</v>
+        <v>-25.9</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>60</v>
@@ -4230,50 +4242,50 @@
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>403.5</v>
+        <v>2744.3</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>389.3</v>
+        <v>2744.3</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>385.41</v>
+        <v>2716.86</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>393.19</v>
+        <v>2771.74</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>369.835</v>
+        <v>2607.085</v>
       </c>
       <c r="AH25" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>420.444</v>
+        <v>2963.844000000001</v>
       </c>
       <c r="AJ25" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>447.695</v>
+        <v>3155.945</v>
       </c>
       <c r="AL25" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM25" s="3" t="n">
-        <v>402.8</v>
+        <v>2875.8</v>
       </c>
       <c r="AN25" s="3" t="n">
-        <v>0.17</v>
+        <v>-0.82</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AP25" s="3" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AQ25" s="3" t="n">
         <v>0</v>
@@ -4286,19 +4298,19 @@
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>R1-BRITANNIA-IND-20260804-1de7ba</t>
+          <t>R1-KOTAKBANK-IND-20260804-5087ff</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA_IND_20260804</t>
+          <t>KOTAKBANK_IND_20260804</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4318,10 +4330,14 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4330,27 +4346,41 @@
       <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="3" t="inlineStr"/>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="inlineStr"/>
-      <c r="R26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟡 WAIT (Δ+1.6%) · Rank → 5→5 · Conf 71% · momentum → · band STRONG · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="3" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
@@ -4358,7 +4388,7 @@
         </is>
       </c>
       <c r="W26" s="3" t="n">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
@@ -4376,46 +4406,46 @@
         </is>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>5406</v>
+        <v>399.65</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>5406</v>
+        <v>389.3</v>
       </c>
       <c r="AE26" s="3" t="n">
-        <v>5351.94</v>
+        <v>385.41</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>5460.06</v>
+        <v>393.19</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>5135.7</v>
+        <v>369.835</v>
       </c>
       <c r="AH26" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>5838.48</v>
+        <v>420.444</v>
       </c>
       <c r="AJ26" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>6216.9</v>
+        <v>447.695</v>
       </c>
       <c r="AL26" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM26" s="3" t="n">
-        <v>5365</v>
+        <v>403.5</v>
       </c>
       <c r="AN26" s="3" t="n">
-        <v>0.37</v>
+        <v>-0.95</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AP26" s="3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AQ26" s="3" t="n">
         <v>0</v>
@@ -4428,19 +4458,19 @@
       </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>R1-TATAPOWER-IND-20260804-dafbb4</t>
+          <t>R1-BRITANNIA-IND-20260804-1de7ba</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER_IND_20260804</t>
+          <t>BRITANNIA_IND_20260804</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4460,14 +4490,10 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4476,10 +4502,10 @@
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0</v>
@@ -4491,12 +4517,12 @@
       <c r="R27" s="3" t="inlineStr"/>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
@@ -4504,7 +4530,7 @@
         </is>
       </c>
       <c r="W27" s="3" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="X27" s="3" t="inlineStr"/>
       <c r="Y27" s="3" t="n">
@@ -4522,40 +4548,40 @@
         </is>
       </c>
       <c r="AC27" s="3" t="n">
-        <v>381.6</v>
+        <v>5406</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>381.6</v>
+        <v>5406</v>
       </c>
       <c r="AE27" s="3" t="n">
-        <v>377.78</v>
+        <v>5351.94</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>385.42</v>
+        <v>5460.06</v>
       </c>
       <c r="AG27" s="3" t="n">
-        <v>362.52</v>
+        <v>5135.7</v>
       </c>
       <c r="AH27" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>412.128</v>
+        <v>5838.48</v>
       </c>
       <c r="AJ27" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>438.84</v>
+        <v>6216.9</v>
       </c>
       <c r="AL27" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM27" s="3" t="n">
-        <v>374.3</v>
+        <v>5385</v>
       </c>
       <c r="AN27" s="3" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>0</v>
@@ -4574,12 +4600,158 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 03:08</t>
+          <t>2026-08-25 05:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>R1-TATAPOWER-IND-20260804-dafbb4</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER_IND_20260804</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>INDIA</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr"/>
+      <c r="J28" s="3" t="inlineStr"/>
+      <c r="K28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="inlineStr"/>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="X28" s="3" t="inlineStr"/>
+      <c r="Y28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>61</v>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="AD28" s="3" t="n">
+        <v>381.6</v>
+      </c>
+      <c r="AE28" s="3" t="n">
+        <v>377.78</v>
+      </c>
+      <c r="AF28" s="3" t="n">
+        <v>385.42</v>
+      </c>
+      <c r="AG28" s="3" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="AH28" s="3" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>412.128</v>
+      </c>
+      <c r="AJ28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK28" s="3" t="n">
+        <v>438.84</v>
+      </c>
+      <c r="AL28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AM28" s="3" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="AN28" s="3" t="n">
+        <v>-0.79</v>
+      </c>
+      <c r="AO28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" s="3" t="inlineStr"/>
+      <c r="AS28" s="3" t="inlineStr"/>
+      <c r="AT28" s="3" t="inlineStr"/>
+      <c r="AU28" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25 05:02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV27"/>
+  <autoFilter ref="A1:AV28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/telegram/aegis_daily_2026-08-25.xlsx
+++ b/reports/telegram/aegis_daily_2026-08-25.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS Daily" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AEGIS Daily'!$A$1:$AV$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV28"/>
+  <dimension ref="A1:AV27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -775,7 +775,7 @@
       <c r="L2" s="3" t="inlineStr"/>
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="O2" s="3" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="W2" s="3" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="X2" s="3" t="n">
         <v>1</v>
@@ -886,19 +886,19 @@
       </c>
       <c r="AV2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>R2-TATACOMM-IND-20260825-759557</t>
+          <t>R1-ICICIBANK-IND-20260804-bfcaee</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>TATACOMM_IND_20260825</t>
+          <t>ICICIBANK_IND_20260804</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -913,60 +913,48 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>TATACOMM</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
+          <t>ICICIBANK</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>ICICI Bank</t>
+        </is>
+      </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>EXIT</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>→ GNFC.NS · +57.6pp alpha</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0</v>
-      </c>
+          <t>STRONG BUY</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="n">
-        <v>52</v>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>🔴</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank #11 · Conf 22% · band EXIT · 60d left · → EXIT (rotate to GNFC.NS)</t>
+          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 82% · momentum → · 91d left · → STRONG BUY</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="n">
-        <v>21.5</v>
+        <v>82</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -974,63 +962,61 @@
         </is>
       </c>
       <c r="W3" s="3" t="n">
-        <v>-23.2</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>1</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="X3" s="3" t="inlineStr"/>
       <c r="Y3" s="3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z3" s="3" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="AA3" s="3" t="n">
-        <v>60</v>
+        <v>91</v>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC3" s="3" t="n">
-        <v>1702.7</v>
+        <v>1417.9</v>
       </c>
       <c r="AD3" s="3" t="n">
-        <v>1702.7</v>
+        <v>1438.5</v>
       </c>
       <c r="AE3" s="3" t="n">
-        <v>1685.67</v>
+        <v>1379</v>
       </c>
       <c r="AF3" s="3" t="n">
-        <v>1719.73</v>
+        <v>1457</v>
       </c>
       <c r="AG3" s="3" t="n">
-        <v>1617.57</v>
+        <v>1347.005</v>
       </c>
       <c r="AH3" s="3" t="n">
-        <v>-5</v>
+        <v>-6.36</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>1838.92</v>
+        <v>1493</v>
       </c>
       <c r="AJ3" s="3" t="n">
-        <v>8</v>
+        <v>3.79</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>1958.1</v>
+        <v>1597.51</v>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>15</v>
+        <v>11.05</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1660</v>
+        <v>1420.5</v>
       </c>
       <c r="AN3" s="3" t="n">
-        <v>2.57</v>
+        <v>-0.18</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="AP3" s="3" t="n">
         <v>0</v>
@@ -1038,31 +1024,33 @@
       <c r="AQ3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr"/>
-      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="AU3" s="3" t="n">
-        <v>57.58</v>
+        <v>3.79</v>
       </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>R1-ICICIBANK-IND-20260804-bfcaee</t>
+          <t>R1-SUNPHARMA-IND-20260804-22e939</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK_IND_20260804</t>
+          <t>SUNPHARMA_IND_20260804</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1082,12 +1070,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ICICI Bank</t>
+          <t>Sun Pharma</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -1098,13 +1086,13 @@
       <c r="I4" s="3" t="inlineStr"/>
       <c r="J4" s="3" t="inlineStr"/>
       <c r="K4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L4" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="M4" s="3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
@@ -1113,12 +1101,16 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.7%) · Rank ↑ 2→1 · Conf 82% · momentum → · 91d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 87% · momentum → · 91d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
       <c r="U4" s="3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1126,7 +1118,7 @@
         </is>
       </c>
       <c r="W4" s="3" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
       <c r="Y4" s="3" t="n">
@@ -1144,43 +1136,43 @@
         </is>
       </c>
       <c r="AC4" s="3" t="n">
-        <v>1417.9</v>
+        <v>1912.7</v>
       </c>
       <c r="AD4" s="3" t="n">
-        <v>1438.5</v>
+        <v>2014.8</v>
       </c>
       <c r="AE4" s="3" t="n">
-        <v>1379</v>
+        <v>1861</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>1457</v>
+        <v>1964</v>
       </c>
       <c r="AG4" s="3" t="n">
-        <v>1347.005</v>
+        <v>1817.065</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>-6.36</v>
+        <v>-9.81</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>1493</v>
+        <v>2000</v>
       </c>
       <c r="AJ4" s="3" t="n">
-        <v>3.79</v>
+        <v>-0.73</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>1597.51</v>
+        <v>2140</v>
       </c>
       <c r="AL4" s="3" t="n">
-        <v>11.05</v>
+        <v>6.21</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1420.5</v>
+        <v>1902.4</v>
       </c>
       <c r="AN4" s="3" t="n">
-        <v>-0.18</v>
+        <v>0.54</v>
       </c>
       <c r="AO4" s="3" t="n">
-        <v>-1.43</v>
+        <v>-5.07</v>
       </c>
       <c r="AP4" s="3" t="n">
         <v>0</v>
@@ -1191,30 +1183,30 @@
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="AT4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU4" s="3" t="n">
-        <v>3.79</v>
+        <v>-0.73</v>
       </c>
       <c r="AV4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>R1-SUNPHARMA-IND-20260804-22e939</t>
+          <t>R1-PIDILITIND-IND-20260804-c2e1ef</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA_IND_20260804</t>
+          <t>PIDILITIND_IND_20260804</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1234,12 +1226,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Sun Pharma</t>
+          <t>Pidilite</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1250,13 +1242,13 @@
       <c r="I5" s="3" t="inlineStr"/>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
@@ -1265,16 +1257,12 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.6%) · Rank ↓ 1→2 · Conf 87% · momentum → · 91d left · → STRONG BUY</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.1% ≤ -5.0% · exit</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-3.1%) · Rank → 3→3 · Conf 86% · momentum → · 91d left · → STRONG BUY</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr"/>
       <c r="U5" s="3" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
@@ -1282,7 +1270,7 @@
         </is>
       </c>
       <c r="W5" s="3" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="X5" s="3" t="inlineStr"/>
       <c r="Y5" s="3" t="n">
@@ -1300,43 +1288,43 @@
         </is>
       </c>
       <c r="AC5" s="3" t="n">
-        <v>1912.7</v>
+        <v>1654.9</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>2014.8</v>
+        <v>1625.5</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>1861</v>
+        <v>1602</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>1964</v>
+        <v>1708</v>
       </c>
       <c r="AG5" s="3" t="n">
-        <v>1817.065</v>
+        <v>1572.155</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>-9.81</v>
+        <v>-3.28</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>2000</v>
+        <v>1677</v>
       </c>
       <c r="AJ5" s="3" t="n">
-        <v>-0.73</v>
+        <v>3.17</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>2140</v>
+        <v>1794.39</v>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>6.21</v>
+        <v>10.39</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1902.4</v>
+        <v>1646</v>
       </c>
       <c r="AN5" s="3" t="n">
         <v>0.54</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>-5.07</v>
+        <v>1.81</v>
       </c>
       <c r="AP5" s="3" t="n">
         <v>0</v>
@@ -1347,30 +1335,30 @@
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="AT5" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>-0.73</v>
+        <v>3.17</v>
       </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>R1-PIDILITIND-IND-20260804-c2e1ef</t>
+          <t>R1-NTPC-IND-20260804-11a3e5</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND_IND_20260804</t>
+          <t>NTPC_IND_20260804</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1390,26 +1378,26 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Pidilite</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>STRONG BUY</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M6" s="3" t="n">
         <v>0</v>
@@ -1421,12 +1409,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.1%) · Rank → 3→3 · Conf 86% · momentum → · 91d left · → STRONG BUY</t>
+          <t>🟢 BUY (Δ-2.3%) · Rank → 4→4 · Conf 71% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="n">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1434,7 +1422,7 @@
         </is>
       </c>
       <c r="W6" s="3" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="X6" s="3" t="inlineStr"/>
       <c r="Y6" s="3" t="n">
@@ -1452,43 +1440,43 @@
         </is>
       </c>
       <c r="AC6" s="3" t="n">
-        <v>1654.9</v>
+        <v>338</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>1625.5</v>
+        <v>345.75</v>
       </c>
       <c r="AE6" s="3" t="n">
-        <v>1602</v>
+        <v>330</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>1708</v>
+        <v>346</v>
       </c>
       <c r="AG6" s="3" t="n">
-        <v>1572.155</v>
+        <v>321.1</v>
       </c>
       <c r="AH6" s="3" t="n">
-        <v>-3.28</v>
+        <v>-7.13</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>1677</v>
+        <v>365.04</v>
       </c>
       <c r="AJ6" s="3" t="n">
-        <v>3.17</v>
+        <v>5.58</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>1794.39</v>
+        <v>390.5928000000001</v>
       </c>
       <c r="AL6" s="3" t="n">
-        <v>10.39</v>
+        <v>12.97</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>1646</v>
+        <v>340.7</v>
       </c>
       <c r="AN6" s="3" t="n">
-        <v>0.54</v>
+        <v>-0.79</v>
       </c>
       <c r="AO6" s="3" t="n">
-        <v>1.81</v>
+        <v>-2.24</v>
       </c>
       <c r="AP6" s="3" t="n">
         <v>0</v>
@@ -1499,30 +1487,30 @@
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="AT6" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>3.17</v>
+        <v>5.58</v>
       </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>R1-NTPC-IND-20260804-11a3e5</t>
+          <t>R1-LUPIN-IND-20260805-6a4927</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>NTPC_IND_20260804</t>
+          <t>LUPIN_IND_20260805</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1542,12 +1530,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>Lupin</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -1558,13 +1546,13 @@
       <c r="I7" s="3" t="inlineStr"/>
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
@@ -1573,12 +1561,16 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.3%) · Rank → 4→4 · Conf 71% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→5 · Conf 67% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-10.0% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
       <c r="U7" s="3" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -1586,11 +1578,11 @@
         </is>
       </c>
       <c r="W7" s="3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="X7" s="3" t="inlineStr"/>
       <c r="Y7" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z7" s="3" t="n">
         <v>90</v>
@@ -1600,50 +1592,50 @@
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC7" s="3" t="n">
-        <v>338</v>
+        <v>2175.4</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>345.75</v>
+        <v>2417</v>
       </c>
       <c r="AE7" s="3" t="n">
-        <v>330</v>
+        <v>2119</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>346</v>
+        <v>2232</v>
       </c>
       <c r="AG7" s="3" t="n">
-        <v>321.1</v>
+        <v>2066.63</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>-7.13</v>
+        <v>-14.5</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>365.04</v>
+        <v>2349.432</v>
       </c>
       <c r="AJ7" s="3" t="n">
-        <v>5.58</v>
+        <v>-2.8</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>390.5928000000001</v>
+        <v>2513.892240000001</v>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>12.97</v>
+        <v>4.01</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>340.7</v>
+        <v>2199.8</v>
       </c>
       <c r="AN7" s="3" t="n">
-        <v>-0.79</v>
+        <v>-1.11</v>
       </c>
       <c r="AO7" s="3" t="n">
-        <v>-2.24</v>
+        <v>-10</v>
       </c>
       <c r="AP7" s="3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ7" s="3" t="n">
         <v>0</v>
@@ -1651,30 +1643,30 @@
       <c r="AR7" s="3" t="inlineStr"/>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Pharma</t>
         </is>
       </c>
       <c r="AT7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>5.58</v>
+        <v>-2.8</v>
       </c>
       <c r="AV7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>R1-LUPIN-IND-20260805-6a4927</t>
+          <t>R1-BEL-IND-20260804-5cc411</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260805</t>
+          <t>BEL_IND_20260804</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1694,12 +1686,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Lupin</t>
+          <t>Bharat Electronics</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -1710,13 +1702,13 @@
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
@@ -1725,16 +1717,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank ↓ 3→5 · Conf 67% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-10.0% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-3.0%) · Rank ↑ 8→6 · Conf 66% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr"/>
       <c r="U8" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -1742,11 +1730,11 @@
         </is>
       </c>
       <c r="W8" s="3" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="X8" s="3" t="inlineStr"/>
       <c r="Y8" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>90</v>
@@ -1756,50 +1744,50 @@
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC8" s="3" t="n">
-        <v>2175.4</v>
+        <v>408.3</v>
       </c>
       <c r="AD8" s="3" t="n">
-        <v>2417</v>
+        <v>388.7</v>
       </c>
       <c r="AE8" s="3" t="n">
-        <v>2119</v>
+        <v>396</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>2232</v>
+        <v>421</v>
       </c>
       <c r="AG8" s="3" t="n">
-        <v>2066.63</v>
+        <v>387.885</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>-14.5</v>
+        <v>-0.21</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>2349.432</v>
+        <v>440.9640000000001</v>
       </c>
       <c r="AJ8" s="3" t="n">
-        <v>-2.8</v>
+        <v>13.45</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>2513.892240000001</v>
+        <v>471.8314800000001</v>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>4.01</v>
+        <v>21.39</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>2199.8</v>
+        <v>414.3</v>
       </c>
       <c r="AN8" s="3" t="n">
-        <v>-1.11</v>
+        <v>-1.45</v>
       </c>
       <c r="AO8" s="3" t="n">
-        <v>-10</v>
+        <v>5.04</v>
       </c>
       <c r="AP8" s="3" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ8" s="3" t="n">
         <v>0</v>
@@ -1807,30 +1795,30 @@
       <c r="AR8" s="3" t="inlineStr"/>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>Pharma</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="AT8" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU8" s="3" t="n">
-        <v>-2.8</v>
+        <v>13.45</v>
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>R1-BEL-IND-20260804-5cc411</t>
+          <t>R1-POWERGRID-IND-20260805-486b96</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BEL_IND_20260804</t>
+          <t>POWERGRID_IND_20260805</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1850,12 +1838,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Bharat Electronics</t>
+          <t>Power Grid</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
@@ -1866,13 +1854,13 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
@@ -1881,12 +1869,16 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank ↑ 8→6 · Conf 66% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.5%) · Rank → 7→7 · Conf 69% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
       <c r="U9" s="3" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
@@ -1898,7 +1890,7 @@
       </c>
       <c r="X9" s="3" t="inlineStr"/>
       <c r="Y9" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>90</v>
@@ -1908,47 +1900,47 @@
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC9" s="3" t="n">
-        <v>408.3</v>
+        <v>270.2</v>
       </c>
       <c r="AD9" s="3" t="n">
-        <v>388.7</v>
+        <v>285.9</v>
       </c>
       <c r="AE9" s="3" t="n">
-        <v>396</v>
+        <v>264</v>
       </c>
       <c r="AF9" s="3" t="n">
-        <v>421</v>
+        <v>277</v>
       </c>
       <c r="AG9" s="3" t="n">
-        <v>387.885</v>
+        <v>256.69</v>
       </c>
       <c r="AH9" s="3" t="n">
-        <v>-0.21</v>
+        <v>-10.22</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>440.9640000000001</v>
+        <v>291.816</v>
       </c>
       <c r="AJ9" s="3" t="n">
-        <v>13.45</v>
+        <v>2.07</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>471.8314800000001</v>
+        <v>312.24312</v>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>21.39</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>414.3</v>
+        <v>274</v>
       </c>
       <c r="AN9" s="3" t="n">
-        <v>-1.45</v>
+        <v>-1.39</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>5.04</v>
+        <v>-5.49</v>
       </c>
       <c r="AP9" s="3" t="n">
         <v>0</v>
@@ -1959,30 +1951,30 @@
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="AT9" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>13.45</v>
+        <v>2.07</v>
       </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>R1-POWERGRID-IND-20260805-486b96</t>
+          <t>R1-ONGC-IND-20260811-f86a0f</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID_IND_20260805</t>
+          <t>ONGC_IND_20260811</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -2002,14 +1994,10 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Power Grid</t>
-        </is>
-      </c>
+          <t>ONGC</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
           <t>BUY</t>
@@ -2018,14 +2006,10 @@
       <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr"/>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
@@ -2033,16 +2017,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.5%) · Rank → 7→7 · Conf 69% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.5% ≤ -5.0% · exit</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-2.9%) · Rank #8 · Conf 67% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr"/>
       <c r="U10" s="3" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2050,11 +2030,11 @@
         </is>
       </c>
       <c r="W10" s="3" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="X10" s="3" t="inlineStr"/>
       <c r="Y10" s="3" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>90</v>
@@ -2064,81 +2044,77 @@
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AC10" s="3" t="n">
-        <v>270.2</v>
+        <v>235.9</v>
       </c>
       <c r="AD10" s="3" t="n">
-        <v>285.9</v>
+        <v>239.4499969482422</v>
       </c>
       <c r="AE10" s="3" t="n">
-        <v>264</v>
+        <v>229</v>
       </c>
       <c r="AF10" s="3" t="n">
-        <v>277</v>
+        <v>243</v>
       </c>
       <c r="AG10" s="3" t="n">
-        <v>256.69</v>
+        <v>224.105</v>
       </c>
       <c r="AH10" s="3" t="n">
-        <v>-10.22</v>
+        <v>-6.41</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>291.816</v>
+        <v>254.772</v>
       </c>
       <c r="AJ10" s="3" t="n">
-        <v>2.07</v>
+        <v>6.4</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>312.24312</v>
+        <v>272.6060400000001</v>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>9.210000000000001</v>
+        <v>13.85</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="AN10" s="3" t="n">
-        <v>-1.39</v>
+        <v>-0.48</v>
       </c>
       <c r="AO10" s="3" t="n">
-        <v>-5.49</v>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-1.48</v>
+      </c>
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>Power</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="AT10" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>2.07</v>
+        <v>6.4</v>
       </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>R1-ONGC-IND-20260811-f86a0f</t>
+          <t>R1-IRCTC-IND-20260804-9c1ab0</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>ONGC_IND_20260811</t>
+          <t>IRCTC_IND_20260804</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -2158,22 +2134,30 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>ONGC</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
+          <t>IRCTC</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>IRCTC</t>
+        </is>
+      </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
       <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>2</v>
+      </c>
       <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
@@ -2181,12 +2165,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank #8 · Conf 67% · momentum → · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 7→9 · Conf 66% · momentum → · 91d left · → HOLD</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr"/>
       <c r="U11" s="3" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -2194,11 +2178,11 @@
         </is>
       </c>
       <c r="W11" s="3" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X11" s="3" t="inlineStr"/>
       <c r="Y11" s="3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>90</v>
@@ -2208,77 +2192,81 @@
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>235.9</v>
+        <v>483.5</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>239.4499969482422</v>
+        <v>494.35</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>229</v>
+        <v>469</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>243</v>
+        <v>498</v>
       </c>
       <c r="AG11" s="3" t="n">
-        <v>224.105</v>
+        <v>459.325</v>
       </c>
       <c r="AH11" s="3" t="n">
-        <v>-6.41</v>
+        <v>-7.09</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>254.772</v>
+        <v>522.1800000000001</v>
       </c>
       <c r="AJ11" s="3" t="n">
-        <v>6.4</v>
+        <v>5.63</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>272.6060400000001</v>
+        <v>558.7326</v>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>13.85</v>
+        <v>13.02</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>237</v>
+        <v>484.2</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>-0.48</v>
+        <v>-0.14</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>-1.48</v>
-      </c>
-      <c r="AP11" s="3" t="inlineStr"/>
-      <c r="AQ11" s="3" t="inlineStr"/>
+        <v>-2.19</v>
+      </c>
+      <c r="AP11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR11" s="3" t="inlineStr"/>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Transport</t>
         </is>
       </c>
       <c r="AT11" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>6.4</v>
+        <v>5.63</v>
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>R1-IRCTC-IND-20260804-9c1ab0</t>
+          <t>R1-COALINDIA-IND-20260805-292818</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>IRCTC_IND_20260804</t>
+          <t>COALINDIA_IND_20260805</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2298,29 +2286,29 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>Coal India</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
       <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
@@ -2329,7 +2317,7 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank ↓ 7→9 · Conf 66% · momentum → · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-2.9%) · Rank → 10→10 · Conf 66% · momentum → · 91d left · → BUY</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr"/>
@@ -2342,11 +2330,11 @@
         </is>
       </c>
       <c r="W12" s="3" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="X12" s="3" t="inlineStr"/>
       <c r="Y12" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>90</v>
@@ -2356,81 +2344,81 @@
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC12" s="3" t="n">
-        <v>483.5</v>
+        <v>405.8</v>
       </c>
       <c r="AD12" s="3" t="n">
-        <v>494.35</v>
+        <v>411.3</v>
       </c>
       <c r="AE12" s="3" t="n">
-        <v>469</v>
+        <v>394</v>
       </c>
       <c r="AF12" s="3" t="n">
-        <v>498</v>
+        <v>418</v>
       </c>
       <c r="AG12" s="3" t="n">
-        <v>459.325</v>
+        <v>385.51</v>
       </c>
       <c r="AH12" s="3" t="n">
-        <v>-7.09</v>
+        <v>-6.27</v>
       </c>
       <c r="AI12" s="3" t="n">
-        <v>522.1800000000001</v>
+        <v>438.2640000000001</v>
       </c>
       <c r="AJ12" s="3" t="n">
-        <v>5.63</v>
+        <v>6.56</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>558.7326</v>
+        <v>468.9424800000001</v>
       </c>
       <c r="AL12" s="3" t="n">
-        <v>13.02</v>
+        <v>14.01</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>484.2</v>
+        <v>406</v>
       </c>
       <c r="AN12" s="3" t="n">
-        <v>-0.14</v>
+        <v>-0.05</v>
       </c>
       <c r="AO12" s="3" t="n">
-        <v>-2.19</v>
+        <v>-1.34</v>
       </c>
       <c r="AP12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="AR12" s="3" t="inlineStr"/>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="AT12" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>5.63</v>
+        <v>6.56</v>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>R1-COALINDIA-IND-20260805-292818</t>
+          <t>R1-ITC-IND-20260805-bb820d</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260805</t>
+          <t>ITC_IND_20260805</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2450,12 +2438,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>Coal India</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
@@ -2466,14 +2454,10 @@
       <c r="I13" s="3" t="inlineStr"/>
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M13" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
@@ -2481,12 +2465,16 @@
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.9%) · Rank → 10→10 · Conf 66% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr"/>
+          <t>🟢 BUY (Δ-2.2%) · Rank #11 · Conf 70% · momentum → · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.3% ≤ -5.0% · exit</t>
+        </is>
+      </c>
       <c r="U13" s="3" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -2512,77 +2500,77 @@
         </is>
       </c>
       <c r="AC13" s="3" t="n">
-        <v>405.8</v>
+        <v>268</v>
       </c>
       <c r="AD13" s="3" t="n">
-        <v>411.3</v>
+        <v>282.9</v>
       </c>
       <c r="AE13" s="3" t="n">
-        <v>394</v>
+        <v>262</v>
       </c>
       <c r="AF13" s="3" t="n">
-        <v>418</v>
+        <v>274</v>
       </c>
       <c r="AG13" s="3" t="n">
-        <v>385.51</v>
+        <v>254.6</v>
       </c>
       <c r="AH13" s="3" t="n">
-        <v>-6.27</v>
+        <v>-10</v>
       </c>
       <c r="AI13" s="3" t="n">
-        <v>438.2640000000001</v>
+        <v>269</v>
       </c>
       <c r="AJ13" s="3" t="n">
-        <v>6.56</v>
+        <v>-4.91</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>468.9424800000001</v>
+        <v>287.83</v>
       </c>
       <c r="AL13" s="3" t="n">
-        <v>14.01</v>
+        <v>1.74</v>
       </c>
       <c r="AM13" s="3" t="n">
-        <v>406</v>
+        <v>270.6</v>
       </c>
       <c r="AN13" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.96</v>
       </c>
       <c r="AO13" s="3" t="n">
-        <v>-1.34</v>
+        <v>-5.27</v>
       </c>
       <c r="AP13" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AQ13" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR13" s="3" t="inlineStr"/>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="AT13" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>6.56</v>
+        <v>-4.91</v>
       </c>
       <c r="AV13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>R1-ITC-IND-20260805-bb820d</t>
+          <t>R1-HINDUNILVR-IND-20260812-d25c10</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260805</t>
+          <t>HINDUNILVR_IND_20260812</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2602,23 +2590,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
+          <t>HINDUNILVR</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
       <c r="J14" s="3" t="inlineStr"/>
       <c r="K14" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L14" s="3" t="inlineStr"/>
       <c r="M14" s="3" t="inlineStr"/>
@@ -2629,16 +2613,12 @@
       <c r="R14" s="3" t="inlineStr"/>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.2%) · Rank #11 · Conf 70% · momentum → · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.3% ≤ -5.0% · exit</t>
-        </is>
-      </c>
+          <t>🟢 BUY (Δ-3.0%) · Rank #12 · Conf 65% · momentum → · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
       <c r="U14" s="3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -2646,11 +2626,11 @@
         </is>
       </c>
       <c r="W14" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="X14" s="3" t="inlineStr"/>
       <c r="Y14" s="3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Z14" s="3" t="n">
         <v>90</v>
@@ -2660,54 +2640,50 @@
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AC14" s="3" t="n">
-        <v>268</v>
+        <v>2019.3</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>282.9</v>
+        <v>2064.89990234375</v>
       </c>
       <c r="AE14" s="3" t="n">
-        <v>262</v>
+        <v>1958</v>
       </c>
       <c r="AF14" s="3" t="n">
-        <v>274</v>
+        <v>2081</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>254.6</v>
+        <v>1918.335</v>
       </c>
       <c r="AH14" s="3" t="n">
-        <v>-10</v>
+        <v>-7.1</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>269</v>
+        <v>2180.844</v>
       </c>
       <c r="AJ14" s="3" t="n">
-        <v>-4.91</v>
+        <v>5.61</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>287.83</v>
+        <v>2333.50308</v>
       </c>
       <c r="AL14" s="3" t="n">
-        <v>1.74</v>
+        <v>13.01</v>
       </c>
       <c r="AM14" s="3" t="n">
-        <v>270.6</v>
+        <v>2019.9</v>
       </c>
       <c r="AN14" s="3" t="n">
-        <v>-0.96</v>
+        <v>-0.03</v>
       </c>
       <c r="AO14" s="3" t="n">
-        <v>-5.27</v>
-      </c>
-      <c r="AP14" s="3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AQ14" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>-2.21</v>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr"/>
       <c r="AS14" s="3" t="inlineStr">
         <is>
@@ -2718,23 +2694,23 @@
         <v>5</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>-4.91</v>
+        <v>5.61</v>
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>R1-HINDUNILVR-IND-20260812-d25c10</t>
+          <t>R2-LUPIN-IND-20260804-80ded8</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR_IND_20260812</t>
+          <t>LUPIN_IND_20260804</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2749,15 +2725,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Lupin</t>
+        </is>
+      </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -2766,10 +2746,14 @@
       <c r="I15" s="3" t="inlineStr"/>
       <c r="J15" s="3" t="inlineStr"/>
       <c r="K15" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="N15" s="3" t="inlineStr"/>
       <c r="O15" s="3" t="inlineStr"/>
       <c r="P15" s="3" t="inlineStr"/>
@@ -2777,12 +2761,12 @@
       <c r="R15" s="3" t="inlineStr"/>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.0%) · Rank #12 · Conf 65% · momentum → · 91d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr"/>
       <c r="U15" s="3" t="n">
-        <v>65</v>
+        <v>51.8</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -2790,91 +2774,89 @@
         </is>
       </c>
       <c r="W15" s="3" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="X15" s="3" t="inlineStr"/>
       <c r="Y15" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="AA15" s="3" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC15" s="3" t="n">
-        <v>2019.3</v>
+        <v>2417</v>
       </c>
       <c r="AD15" s="3" t="n">
-        <v>2064.89990234375</v>
+        <v>2417</v>
       </c>
       <c r="AE15" s="3" t="n">
-        <v>1958</v>
+        <v>2392.83</v>
       </c>
       <c r="AF15" s="3" t="n">
-        <v>2081</v>
+        <v>2441.17</v>
       </c>
       <c r="AG15" s="3" t="n">
-        <v>1918.335</v>
+        <v>2296.15</v>
       </c>
       <c r="AH15" s="3" t="n">
-        <v>-7.1</v>
+        <v>-5</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>2180.844</v>
+        <v>2610.36</v>
       </c>
       <c r="AJ15" s="3" t="n">
-        <v>5.61</v>
+        <v>8</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>2333.50308</v>
+        <v>2779.55</v>
       </c>
       <c r="AL15" s="3" t="n">
-        <v>13.01</v>
+        <v>15</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>2019.9</v>
+        <v>2199.8</v>
       </c>
       <c r="AN15" s="3" t="n">
-        <v>-0.03</v>
+        <v>-1.11</v>
       </c>
       <c r="AO15" s="3" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="AP15" s="3" t="inlineStr"/>
-      <c r="AQ15" s="3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AQ15" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="AR15" s="3" t="inlineStr"/>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>FMCG</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="n">
-        <v>5</v>
-      </c>
+      <c r="AS15" s="3" t="inlineStr"/>
+      <c r="AT15" s="3" t="inlineStr"/>
       <c r="AU15" s="3" t="n">
-        <v>5.61</v>
+        <v>8</v>
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>R2-LUPIN-IND-20260804-80ded8</t>
+          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>LUPIN_IND_20260804</t>
+          <t>CHAMBLFERT_IND_20260804</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2894,12 +2876,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Lupin</t>
+          <t>Chambal Fert.</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -2910,13 +2892,13 @@
       <c r="I16" s="3" t="inlineStr"/>
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="inlineStr"/>
@@ -2925,12 +2907,12 @@
       <c r="R16" s="3" t="inlineStr"/>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 52% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr"/>
       <c r="U16" s="3" t="n">
-        <v>51.8</v>
+        <v>38.3</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -2938,7 +2920,7 @@
         </is>
       </c>
       <c r="W16" s="3" t="n">
-        <v>26</v>
+        <v>22.4</v>
       </c>
       <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
@@ -2956,46 +2938,46 @@
         </is>
       </c>
       <c r="AC16" s="3" t="n">
-        <v>2417</v>
+        <v>443.35</v>
       </c>
       <c r="AD16" s="3" t="n">
-        <v>2417</v>
+        <v>443.35</v>
       </c>
       <c r="AE16" s="3" t="n">
-        <v>2392.83</v>
+        <v>438.92</v>
       </c>
       <c r="AF16" s="3" t="n">
-        <v>2441.17</v>
+        <v>447.78</v>
       </c>
       <c r="AG16" s="3" t="n">
-        <v>2296.15</v>
+        <v>421.1825</v>
       </c>
       <c r="AH16" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>2610.36</v>
+        <v>478.818</v>
       </c>
       <c r="AJ16" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>2779.55</v>
+        <v>509.8525</v>
       </c>
       <c r="AL16" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>2199.8</v>
+        <v>431.6</v>
       </c>
       <c r="AN16" s="3" t="n">
-        <v>-1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP16" s="3" t="n">
-        <v>1.24</v>
+        <v>2.54</v>
       </c>
       <c r="AQ16" s="3" t="n">
         <v>0</v>
@@ -3008,19 +2990,19 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>R2-CHAMBLFERT-IND-20260804-5eb424</t>
+          <t>R2-PNB-IND-20260804-c7957c</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT_IND_20260804</t>
+          <t>PNB_IND_20260804</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -3040,12 +3022,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>Chambal Fert.</t>
+          <t>Punjab Natl. Bank</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -3056,13 +3038,13 @@
       <c r="I17" s="3" t="inlineStr"/>
       <c r="J17" s="3" t="inlineStr"/>
       <c r="K17" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
       <c r="O17" s="3" t="inlineStr"/>
@@ -3071,12 +3053,12 @@
       <c r="R17" s="3" t="inlineStr"/>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 3→8 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr"/>
       <c r="U17" s="3" t="n">
-        <v>38.3</v>
+        <v>32.1</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3084,7 +3066,7 @@
         </is>
       </c>
       <c r="W17" s="3" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="X17" s="3" t="inlineStr"/>
       <c r="Y17" s="3" t="n">
@@ -3102,49 +3084,49 @@
         </is>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>443.35</v>
+        <v>113.36</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>443.35</v>
+        <v>113.36</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>438.92</v>
+        <v>112.23</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>447.78</v>
+        <v>114.49</v>
       </c>
       <c r="AG17" s="3" t="n">
-        <v>421.1825</v>
+        <v>107.692</v>
       </c>
       <c r="AH17" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI17" s="3" t="n">
-        <v>478.818</v>
+        <v>122.4288</v>
       </c>
       <c r="AJ17" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>509.8525</v>
+        <v>130.364</v>
       </c>
       <c r="AL17" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>431.6</v>
+        <v>116.5</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>1.4</v>
+        <v>-0.61</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP17" s="3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>0</v>
+        <v>-2.01</v>
       </c>
       <c r="AR17" s="3" t="inlineStr"/>
       <c r="AS17" s="3" t="inlineStr"/>
@@ -3154,19 +3136,19 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>R2-PNB-IND-20260804-c7957c</t>
+          <t>R2-COALINDIA-IND-20260804-12bb5e</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>PNB_IND_20260804</t>
+          <t>COALINDIA_IND_20260804</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -3186,12 +3168,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Punjab Natl. Bank</t>
+          <t>Coal India</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -3202,10 +3184,10 @@
       <c r="I18" s="3" t="inlineStr"/>
       <c r="J18" s="3" t="inlineStr"/>
       <c r="K18" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M18" s="3" t="n">
         <v>0</v>
@@ -3217,12 +3199,12 @@
       <c r="R18" s="3" t="inlineStr"/>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 32% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr"/>
       <c r="U18" s="3" t="n">
-        <v>32.1</v>
+        <v>36.1</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -3248,40 +3230,40 @@
         </is>
       </c>
       <c r="AC18" s="3" t="n">
-        <v>113.36</v>
+        <v>411.3</v>
       </c>
       <c r="AD18" s="3" t="n">
-        <v>113.36</v>
+        <v>411.3</v>
       </c>
       <c r="AE18" s="3" t="n">
-        <v>112.23</v>
+        <v>407.19</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>114.49</v>
+        <v>415.41</v>
       </c>
       <c r="AG18" s="3" t="n">
-        <v>107.692</v>
+        <v>390.735</v>
       </c>
       <c r="AH18" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI18" s="3" t="n">
-        <v>122.4288</v>
+        <v>444.2040000000001</v>
       </c>
       <c r="AJ18" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>130.364</v>
+        <v>472.995</v>
       </c>
       <c r="AL18" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>116.5</v>
+        <v>406</v>
       </c>
       <c r="AN18" s="3" t="n">
-        <v>-0.61</v>
+        <v>-0.05</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>0</v>
@@ -3290,7 +3272,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" s="3" t="n">
-        <v>-2.01</v>
+        <v>-0.3</v>
       </c>
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr"/>
@@ -3300,19 +3282,19 @@
       </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>R2-COALINDIA-IND-20260804-12bb5e</t>
+          <t>R2-ITC-IND-20260804-a049df</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA_IND_20260804</t>
+          <t>ITC_IND_20260804</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -3332,12 +3314,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Coal India</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -3348,13 +3330,13 @@
       <c r="I19" s="3" t="inlineStr"/>
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
       <c r="O19" s="3" t="inlineStr"/>
@@ -3363,12 +3345,12 @@
       <c r="R19" s="3" t="inlineStr"/>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 5→5 · Conf 36% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr"/>
       <c r="U19" s="3" t="n">
-        <v>36.1</v>
+        <v>38.3</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -3376,7 +3358,7 @@
         </is>
       </c>
       <c r="W19" s="3" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="X19" s="3" t="inlineStr"/>
       <c r="Y19" s="3" t="n">
@@ -3394,49 +3376,49 @@
         </is>
       </c>
       <c r="AC19" s="3" t="n">
-        <v>411.3</v>
+        <v>282.9</v>
       </c>
       <c r="AD19" s="3" t="n">
-        <v>411.3</v>
+        <v>282.9</v>
       </c>
       <c r="AE19" s="3" t="n">
-        <v>407.19</v>
+        <v>280.07</v>
       </c>
       <c r="AF19" s="3" t="n">
-        <v>415.41</v>
+        <v>285.73</v>
       </c>
       <c r="AG19" s="3" t="n">
-        <v>390.735</v>
+        <v>268.7549999999999</v>
       </c>
       <c r="AH19" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI19" s="3" t="n">
-        <v>444.2040000000001</v>
+        <v>305.532</v>
       </c>
       <c r="AJ19" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>472.995</v>
+        <v>325.3349999999999</v>
       </c>
       <c r="AL19" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>406</v>
+        <v>270.6</v>
       </c>
       <c r="AN19" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.96</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP19" s="3" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AQ19" s="3" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="AR19" s="3" t="inlineStr"/>
       <c r="AS19" s="3" t="inlineStr"/>
@@ -3446,19 +3428,19 @@
       </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>R2-ITC-IND-20260804-a049df</t>
+          <t>R2-BATAINDIA-IND-20260804-21b729</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ITC_IND_20260804</t>
+          <t>BATAINDIA_IND_20260804</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -3478,12 +3460,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>Bata India</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -3494,13 +3476,13 @@
       <c r="I20" s="3" t="inlineStr"/>
       <c r="J20" s="3" t="inlineStr"/>
       <c r="K20" s="3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="inlineStr"/>
       <c r="O20" s="3" t="inlineStr"/>
@@ -3509,12 +3491,12 @@
       <c r="R20" s="3" t="inlineStr"/>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank ↓ 7→9 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr"/>
       <c r="U20" s="3" t="n">
-        <v>38.3</v>
+        <v>24</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -3522,7 +3504,7 @@
         </is>
       </c>
       <c r="W20" s="3" t="n">
-        <v>21.6</v>
+        <v>-30.3</v>
       </c>
       <c r="X20" s="3" t="inlineStr"/>
       <c r="Y20" s="3" t="n">
@@ -3540,49 +3522,49 @@
         </is>
       </c>
       <c r="AC20" s="3" t="n">
-        <v>282.9</v>
+        <v>709</v>
       </c>
       <c r="AD20" s="3" t="n">
-        <v>282.9</v>
+        <v>709</v>
       </c>
       <c r="AE20" s="3" t="n">
-        <v>280.07</v>
+        <v>701.91</v>
       </c>
       <c r="AF20" s="3" t="n">
-        <v>285.73</v>
+        <v>716.09</v>
       </c>
       <c r="AG20" s="3" t="n">
-        <v>268.7549999999999</v>
+        <v>673.55</v>
       </c>
       <c r="AH20" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI20" s="3" t="n">
-        <v>305.532</v>
+        <v>765.72</v>
       </c>
       <c r="AJ20" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>325.3349999999999</v>
+        <v>815.3499999999999</v>
       </c>
       <c r="AL20" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM20" s="3" t="n">
-        <v>270.6</v>
+        <v>702.35</v>
       </c>
       <c r="AN20" s="3" t="n">
-        <v>-0.96</v>
+        <v>-2.5</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP20" s="3" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AQ20" s="3" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="AR20" s="3" t="inlineStr"/>
       <c r="AS20" s="3" t="inlineStr"/>
@@ -3592,19 +3574,19 @@
       </c>
       <c r="AV20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>R2-BATAINDIA-IND-20260804-21b729</t>
+          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA_IND_20260804</t>
+          <t>PERSISTENT_IND_20260805</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -3624,14 +3606,10 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Bata India</t>
-        </is>
-      </c>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
       <c r="H21" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -3640,10 +3618,10 @@
       <c r="I21" s="3" t="inlineStr"/>
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="M21" s="3" t="n">
         <v>0</v>
@@ -3655,12 +3633,12 @@
       <c r="R21" s="3" t="inlineStr"/>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 15→15 · Conf 24% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr"/>
       <c r="U21" s="3" t="n">
-        <v>24</v>
+        <v>40.7</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -3668,11 +3646,11 @@
         </is>
       </c>
       <c r="W21" s="3" t="n">
-        <v>-30.3</v>
+        <v>23.8</v>
       </c>
       <c r="X21" s="3" t="inlineStr"/>
       <c r="Y21" s="3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>60</v>
@@ -3682,53 +3660,53 @@
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="AC21" s="3" t="n">
-        <v>709</v>
+        <v>5322.4</v>
       </c>
       <c r="AD21" s="3" t="n">
-        <v>709</v>
+        <v>5322.4</v>
       </c>
       <c r="AE21" s="3" t="n">
-        <v>701.91</v>
+        <v>5269.18</v>
       </c>
       <c r="AF21" s="3" t="n">
-        <v>716.09</v>
+        <v>5375.62</v>
       </c>
       <c r="AG21" s="3" t="n">
-        <v>673.55</v>
+        <v>5056.28</v>
       </c>
       <c r="AH21" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI21" s="3" t="n">
-        <v>765.72</v>
+        <v>5748.192</v>
       </c>
       <c r="AJ21" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>815.3499999999999</v>
+        <v>6120.759999999999</v>
       </c>
       <c r="AL21" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM21" s="3" t="n">
-        <v>702.35</v>
+        <v>5693.5</v>
       </c>
       <c r="AN21" s="3" t="n">
-        <v>-2.5</v>
+        <v>-1.36</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP21" s="3" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AQ21" s="3" t="n">
-        <v>-1.5</v>
+        <v>0</v>
       </c>
       <c r="AR21" s="3" t="inlineStr"/>
       <c r="AS21" s="3" t="inlineStr"/>
@@ -3738,19 +3716,19 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>R2-PERSISTENT-IND-20260805-48a8e2</t>
+          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT_IND_20260805</t>
+          <t>BAJAJHLDNG_IND_20260805</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3770,7 +3748,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr"/>
@@ -3782,10 +3760,10 @@
       <c r="I22" s="3" t="inlineStr"/>
       <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>0</v>
@@ -3797,12 +3775,12 @@
       <c r="R22" s="3" t="inlineStr"/>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 4→4 · Conf 41% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr"/>
       <c r="U22" s="3" t="n">
-        <v>40.7</v>
+        <v>38.3</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
@@ -3810,7 +3788,7 @@
         </is>
       </c>
       <c r="W22" s="3" t="n">
-        <v>23.8</v>
+        <v>20.7</v>
       </c>
       <c r="X22" s="3" t="inlineStr"/>
       <c r="Y22" s="3" t="n">
@@ -3828,46 +3806,46 @@
         </is>
       </c>
       <c r="AC22" s="3" t="n">
-        <v>5322.4</v>
+        <v>11127</v>
       </c>
       <c r="AD22" s="3" t="n">
-        <v>5322.4</v>
+        <v>11127</v>
       </c>
       <c r="AE22" s="3" t="n">
-        <v>5269.18</v>
+        <v>11015.73</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>5375.62</v>
+        <v>11238.27</v>
       </c>
       <c r="AG22" s="3" t="n">
-        <v>5056.28</v>
+        <v>10570.65</v>
       </c>
       <c r="AH22" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI22" s="3" t="n">
-        <v>5748.192</v>
+        <v>12017.16</v>
       </c>
       <c r="AJ22" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK22" s="3" t="n">
-        <v>6120.759999999999</v>
+        <v>12796.05</v>
       </c>
       <c r="AL22" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM22" s="3" t="n">
-        <v>5693.5</v>
+        <v>11250</v>
       </c>
       <c r="AN22" s="3" t="n">
-        <v>-1.36</v>
+        <v>-0.97</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP22" s="3" t="n">
-        <v>3.32</v>
+        <v>3.69</v>
       </c>
       <c r="AQ22" s="3" t="n">
         <v>0</v>
@@ -3880,19 +3858,19 @@
       </c>
       <c r="AV22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>R2-BAJAJHLDNG-IND-20260805-660791</t>
+          <t>R2-LICI-IND-20260805-a4f409</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG_IND_20260805</t>
+          <t>LICI_IND_20260805</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3912,7 +3890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr"/>
@@ -3924,14 +3902,10 @@
       <c r="I23" s="3" t="inlineStr"/>
       <c r="J23" s="3" t="inlineStr"/>
       <c r="K23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="L23" s="3" t="inlineStr"/>
+      <c r="M23" s="3" t="inlineStr"/>
       <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="inlineStr"/>
       <c r="P23" s="3" t="inlineStr"/>
@@ -3939,12 +3913,12 @@
       <c r="R23" s="3" t="inlineStr"/>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 10→10 · Conf 38% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr"/>
       <c r="U23" s="3" t="n">
-        <v>38.3</v>
+        <v>37.2</v>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
@@ -3952,7 +3926,7 @@
         </is>
       </c>
       <c r="W23" s="3" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
@@ -3970,46 +3944,46 @@
         </is>
       </c>
       <c r="AC23" s="3" t="n">
-        <v>11127</v>
+        <v>391.3</v>
       </c>
       <c r="AD23" s="3" t="n">
-        <v>11127</v>
+        <v>391.3</v>
       </c>
       <c r="AE23" s="3" t="n">
-        <v>11015.73</v>
+        <v>387.39</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>11238.27</v>
+        <v>395.21</v>
       </c>
       <c r="AG23" s="3" t="n">
-        <v>10570.65</v>
+        <v>371.735</v>
       </c>
       <c r="AH23" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI23" s="3" t="n">
-        <v>12017.16</v>
+        <v>422.604</v>
       </c>
       <c r="AJ23" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK23" s="3" t="n">
-        <v>12796.05</v>
+        <v>449.995</v>
       </c>
       <c r="AL23" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM23" s="3" t="n">
-        <v>11250</v>
+        <v>426</v>
       </c>
       <c r="AN23" s="3" t="n">
-        <v>-0.97</v>
+        <v>-0.08</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AP23" s="3" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AQ23" s="3" t="n">
         <v>0</v>
@@ -4022,19 +3996,19 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>R2-LICI-IND-20260805-a4f409</t>
+          <t>R2-TIINDIA-IND-20260805-44fbae</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LICI_IND_20260805</t>
+          <t>TIINDIA_IND_20260805</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -4054,7 +4028,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>TIINDIA</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr"/>
@@ -4066,7 +4040,7 @@
       <c r="I24" s="3" t="inlineStr"/>
       <c r="J24" s="3" t="inlineStr"/>
       <c r="K24" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
@@ -4077,12 +4051,12 @@
       <c r="R24" s="3" t="inlineStr"/>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #9 · Conf 37% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr"/>
       <c r="U24" s="3" t="n">
-        <v>37.2</v>
+        <v>21.5</v>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
@@ -4090,7 +4064,7 @@
         </is>
       </c>
       <c r="W24" s="3" t="n">
-        <v>20.6</v>
+        <v>-25.9</v>
       </c>
       <c r="X24" s="3" t="inlineStr"/>
       <c r="Y24" s="3" t="n">
@@ -4108,40 +4082,40 @@
         </is>
       </c>
       <c r="AC24" s="3" t="n">
-        <v>391.3</v>
+        <v>2744.3</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>391.3</v>
+        <v>2744.3</v>
       </c>
       <c r="AE24" s="3" t="n">
-        <v>387.39</v>
+        <v>2716.86</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>395.21</v>
+        <v>2771.74</v>
       </c>
       <c r="AG24" s="3" t="n">
-        <v>371.735</v>
+        <v>2607.085</v>
       </c>
       <c r="AH24" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI24" s="3" t="n">
-        <v>422.604</v>
+        <v>2963.844000000001</v>
       </c>
       <c r="AJ24" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK24" s="3" t="n">
-        <v>449.995</v>
+        <v>3155.945</v>
       </c>
       <c r="AL24" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM24" s="3" t="n">
-        <v>426</v>
+        <v>2875.8</v>
       </c>
       <c r="AN24" s="3" t="n">
-        <v>-0.08</v>
+        <v>-0.82</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>0</v>
@@ -4160,19 +4134,19 @@
       </c>
       <c r="AV24" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>R2-TIINDIA-IND-20260805-44fbae</t>
+          <t>R1-KOTAKBANK-IND-20260804-5087ff</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA_IND_20260805</t>
+          <t>KOTAKBANK_IND_20260804</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -4187,15 +4161,19 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>TIINDIA</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
+          <t>KOTAKBANK</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Kotak Bank</t>
+        </is>
+      </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4204,23 +4182,41 @@
       <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="inlineStr"/>
       <c r="K25" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr"/>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="3" t="inlineStr"/>
-      <c r="R25" s="3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
+        </is>
+      </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #12 · Conf 22% · momentum → · 61d left · → HOLD</t>
+          <t>🟡 WAIT (Δ+1.6%) · Rank → 5→5 · Conf 71% · momentum → · band STRONG · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr"/>
       <c r="U25" s="3" t="n">
-        <v>21.5</v>
+        <v>71</v>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
@@ -4228,11 +4224,11 @@
         </is>
       </c>
       <c r="W25" s="3" t="n">
-        <v>-25.9</v>
+        <v>63</v>
       </c>
       <c r="X25" s="3" t="inlineStr"/>
       <c r="Y25" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z25" s="3" t="n">
         <v>60</v>
@@ -4242,50 +4238,50 @@
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AC25" s="3" t="n">
-        <v>2744.3</v>
+        <v>399.65</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>2744.3</v>
+        <v>389.3</v>
       </c>
       <c r="AE25" s="3" t="n">
-        <v>2716.86</v>
+        <v>385.41</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>2771.74</v>
+        <v>393.19</v>
       </c>
       <c r="AG25" s="3" t="n">
-        <v>2607.085</v>
+        <v>369.835</v>
       </c>
       <c r="AH25" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI25" s="3" t="n">
-        <v>2963.844000000001</v>
+        <v>420.444</v>
       </c>
       <c r="AJ25" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK25" s="3" t="n">
-        <v>3155.945</v>
+        <v>447.695</v>
       </c>
       <c r="AL25" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM25" s="3" t="n">
-        <v>2875.8</v>
+        <v>403.5</v>
       </c>
       <c r="AN25" s="3" t="n">
-        <v>-0.82</v>
+        <v>-0.95</v>
       </c>
       <c r="AO25" s="3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AP25" s="3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AQ25" s="3" t="n">
         <v>0</v>
@@ -4298,19 +4294,19 @@
       </c>
       <c r="AV25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>R1-KOTAKBANK-IND-20260804-5087ff</t>
+          <t>R1-BRITANNIA-IND-20260804-1de7ba</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK_IND_20260804</t>
+          <t>BRITANNIA_IND_20260804</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -4330,14 +4326,10 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>Kotak Bank</t>
-        </is>
-      </c>
+          <t>BRITANNIA</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4346,41 +4338,27 @@
       <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="inlineStr"/>
       <c r="K26" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M26" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="N26" s="3" t="n">
-        <v>84</v>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="Q26" s="3" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 0d (high) (+63 more) → -2.5pts · crude +19.8% (rising) → +1.0pts</t>
-        </is>
-      </c>
+      <c r="N26" s="3" t="inlineStr"/>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr"/>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t>🟡 WAIT (Δ+1.6%) · Rank → 5→5 · Conf 71% · momentum → · band STRONG · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr"/>
       <c r="U26" s="3" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
@@ -4388,7 +4366,7 @@
         </is>
       </c>
       <c r="W26" s="3" t="n">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="X26" s="3" t="inlineStr"/>
       <c r="Y26" s="3" t="n">
@@ -4406,46 +4384,46 @@
         </is>
       </c>
       <c r="AC26" s="3" t="n">
-        <v>399.65</v>
+        <v>5406</v>
       </c>
       <c r="AD26" s="3" t="n">
-        <v>389.3</v>
+        <v>5406</v>
       </c>
       <c r="AE26" s="3" t="n">
-        <v>385.41</v>
+        <v>5351.94</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>393.19</v>
+        <v>5460.06</v>
       </c>
       <c r="AG26" s="3" t="n">
-        <v>369.835</v>
+        <v>5135.7</v>
       </c>
       <c r="AH26" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>420.444</v>
+        <v>5838.48</v>
       </c>
       <c r="AJ26" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK26" s="3" t="n">
-        <v>447.695</v>
+        <v>6216.9</v>
       </c>
       <c r="AL26" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM26" s="3" t="n">
-        <v>403.5</v>
+        <v>5385</v>
       </c>
       <c r="AN26" s="3" t="n">
-        <v>-0.95</v>
+        <v>-1.62</v>
       </c>
       <c r="AO26" s="3" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AP26" s="3" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AQ26" s="3" t="n">
         <v>0</v>
@@ -4458,19 +4436,19 @@
       </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>R1-BRITANNIA-IND-20260804-1de7ba</t>
+          <t>R1-TATAPOWER-IND-20260804-dafbb4</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA_IND_20260804</t>
+          <t>TATAPOWER_IND_20260804</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -4490,10 +4468,14 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
+          <t>TATAPOWER</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Tata Power</t>
+        </is>
+      </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
           <t>HOLD</t>
@@ -4502,10 +4484,10 @@
       <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="inlineStr"/>
       <c r="K27" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>0</v>
@@ -4517,12 +4499,12 @@
       <c r="R27" s="3" t="inlineStr"/>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 9→9 · Conf 66% · momentum → · 61d left · → HOLD</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr"/>
       <c r="U27" s="3" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
@@ -4530,7 +4512,7 @@
         </is>
       </c>
       <c r="W27" s="3" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="X27" s="3" t="inlineStr"/>
       <c r="Y27" s="3" t="n">
@@ -4548,40 +4530,40 @@
         </is>
       </c>
       <c r="AC27" s="3" t="n">
-        <v>5406</v>
+        <v>381.6</v>
       </c>
       <c r="AD27" s="3" t="n">
-        <v>5406</v>
+        <v>381.6</v>
       </c>
       <c r="AE27" s="3" t="n">
-        <v>5351.94</v>
+        <v>377.78</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>5460.06</v>
+        <v>385.42</v>
       </c>
       <c r="AG27" s="3" t="n">
-        <v>5135.7</v>
+        <v>362.52</v>
       </c>
       <c r="AH27" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>5838.48</v>
+        <v>412.128</v>
       </c>
       <c r="AJ27" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AK27" s="3" t="n">
-        <v>6216.9</v>
+        <v>438.84</v>
       </c>
       <c r="AL27" s="3" t="n">
         <v>15</v>
       </c>
       <c r="AM27" s="3" t="n">
-        <v>5385</v>
+        <v>374.3</v>
       </c>
       <c r="AN27" s="3" t="n">
-        <v>-1.62</v>
+        <v>-0.79</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>0</v>
@@ -4600,158 +4582,12 @@
       </c>
       <c r="AV27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 05:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>R1-TATAPOWER-IND-20260804-dafbb4</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER_IND_20260804</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>INDIA</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>TATAPOWER</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>Tata Power</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="3" t="inlineStr"/>
-      <c r="O28" s="3" t="inlineStr"/>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="3" t="inlineStr"/>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 6→6 · Conf 64% · momentum → · 61d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr"/>
-      <c r="U28" s="3" t="n">
-        <v>64</v>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="n">
-        <v>54</v>
-      </c>
-      <c r="X28" s="3" t="inlineStr"/>
-      <c r="Y28" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z28" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA28" s="3" t="n">
-        <v>61</v>
-      </c>
-      <c r="AB28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="AC28" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AD28" s="3" t="n">
-        <v>381.6</v>
-      </c>
-      <c r="AE28" s="3" t="n">
-        <v>377.78</v>
-      </c>
-      <c r="AF28" s="3" t="n">
-        <v>385.42</v>
-      </c>
-      <c r="AG28" s="3" t="n">
-        <v>362.52</v>
-      </c>
-      <c r="AH28" s="3" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AI28" s="3" t="n">
-        <v>412.128</v>
-      </c>
-      <c r="AJ28" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AK28" s="3" t="n">
-        <v>438.84</v>
-      </c>
-      <c r="AL28" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AM28" s="3" t="n">
-        <v>374.3</v>
-      </c>
-      <c r="AN28" s="3" t="n">
-        <v>-0.79</v>
-      </c>
-      <c r="AO28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" s="3" t="inlineStr"/>
-      <c r="AS28" s="3" t="inlineStr"/>
-      <c r="AT28" s="3" t="inlineStr"/>
-      <c r="AU28" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV28" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25 05:02</t>
+          <t>2026-08-25 14:42</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AV28"/>
+  <autoFilter ref="A1:AV27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>